--- a/templates/hanson-full-marathon-beginner-template.xlsx
+++ b/templates/hanson-full-marathon-beginner-template.xlsx
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="G40" s="137" t="n">
-        <v>8.800000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="H40" s="136" t="n"/>
       <c r="I40" s="209" t="n"/>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="G47" s="137" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="H47" s="136" t="n"/>
       <c r="I47" s="209" t="n"/>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G54" s="137" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H54" s="136" t="n"/>
       <c r="I54" s="209" t="n"/>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="G61" s="137" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H61" s="118" t="n"/>
       <c r="I61" s="209" t="n"/>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="G68" s="137" t="n">
-        <v>8.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H68" s="136" t="n"/>
       <c r="I68" s="209" t="n"/>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="G75" s="137" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="H75" s="136" t="n"/>
       <c r="I75" s="209" t="n"/>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="G82" s="137" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="H82" s="118" t="n"/>
       <c r="I82" s="209" t="n"/>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="G89" s="137" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="H89" s="118" t="n"/>
       <c r="I89" s="209" t="n"/>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G96" s="137" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H96" s="118" t="n"/>
       <c r="I96" s="209" t="n"/>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="G103" s="137" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="H103" s="118" t="n"/>
       <c r="I103" s="209" t="n"/>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="G110" s="137" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="H110" s="118" t="n"/>
       <c r="I110" s="209" t="n"/>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="G117" s="137" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="H117" s="118" t="n"/>
       <c r="I117" s="209" t="n"/>
